--- a/20240512_SA_binary/output/system_analysis/system_analysis_main.xlsx
+++ b/20240512_SA_binary/output/system_analysis/system_analysis_main.xlsx
@@ -46,16 +46,16 @@
     <t>CoIn2</t>
   </si>
   <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
+    <t>Mg2Cu</t>
+  </si>
+  <si>
     <t>IrIn3</t>
   </si>
   <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
     <t>RuIn3</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
   </si>
   <si>
     <t>Co-Co</t>
@@ -485,13 +485,13 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>2.608</v>
+        <v>2.597</v>
       </c>
       <c r="G3">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -554,13 +554,13 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>2.597</v>
+        <v>2.708</v>
       </c>
       <c r="G7">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -617,16 +617,16 @@
         <v>2</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>2.62</v>
+        <v>2.608</v>
       </c>
       <c r="G11">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="H11">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -651,7 +651,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -686,10 +686,10 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>2.708</v>
+        <v>2.62</v>
       </c>
       <c r="G15">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="H15">
         <v>0.001</v>
